--- a/SQL/ExcelCauHinh/Settup AXE.xlsx
+++ b/SQL/ExcelCauHinh/Settup AXE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\ToolAXE\CauHinhHeThongAXE\SQL\ExcelCauHinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667FF2AA-A39B-4AA3-A512-C949EFDC21A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0B9549-308B-4421-BE2C-E92E26FF2934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cài đặt IIS" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="109">
   <si>
     <t>Thông tin chung</t>
   </si>
@@ -339,10 +339,22 @@
     <t>AXE_CORE_2026_STG.bak</t>
   </si>
   <si>
-    <t>AXE_CORE_2026_ACC</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CLOUD</t>
+    <t>AXE_CORE_2026_CT_ACC</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CT_CLOUD</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CT_CNF</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CT_LOG</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CT_MSG</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CT_STG</t>
   </si>
 </sst>
 </file>
@@ -631,6 +643,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -640,15 +673,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -657,18 +681,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -988,15 +1000,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
       <c r="G1" s="12"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -1009,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="12"/>
-      <c r="H2" s="40"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -1020,7 +1032,7 @@
       </c>
       <c r="C3" s="17"/>
       <c r="G3" s="12"/>
-      <c r="H3" s="41"/>
+      <c r="H3" s="40"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -1033,7 +1045,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="12"/>
-      <c r="H4" s="41"/>
+      <c r="H4" s="40"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -1044,7 +1056,7 @@
       </c>
       <c r="C5" s="17"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="41"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
@@ -1057,7 +1069,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="12"/>
-      <c r="H6" s="41"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
@@ -1070,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="G7" s="12"/>
-      <c r="H7" s="41"/>
+      <c r="H7" s="40"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
@@ -1081,17 +1093,17 @@
       </c>
       <c r="C8" s="17"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="42"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
       <c r="G9" s="12"/>
       <c r="H9" s="20"/>
     </row>
@@ -1133,13 +1145,13 @@
       <c r="H12" s="21"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
       <c r="F13" s="50"/>
       <c r="G13" s="12"/>
       <c r="H13" s="13"/>
@@ -1203,14 +1215,14 @@
       <c r="H16" s="21"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
       <c r="G17" s="12"/>
       <c r="H17" s="13"/>
     </row>
@@ -1395,14 +1407,14 @@
       <c r="H25" s="21"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
       <c r="H26" s="13"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1439,14 +1451,14 @@
       <c r="H29" s="21"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
+      <c r="A30" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
       <c r="H30" s="21"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1459,11 +1471,11 @@
       <c r="C31" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D31" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
       <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1498,9 +1510,9 @@
         <f t="shared" ref="C33:C37" si="3">$A$11</f>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
       <c r="H33" s="21" t="str">
         <f>IF(C33="","",$B$8&amp;" set app "&amp;A33&amp;"/"&amp;B33&amp;"  /"&amp;"applicationPool:"&amp;C33&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/admin  /applicationPool:AXE_Test-Web</v>
@@ -1518,9 +1530,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
       <c r="H34" s="21" t="str">
         <f>IF(C34="","",$B$8&amp;" set app "&amp;A34&amp;"/"&amp;B34&amp;"  /"&amp;"applicationPool:"&amp;C34&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/resumable  /applicationPool:AXE_Test-Web</v>
@@ -1538,9 +1550,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
       <c r="H35" s="21" t="str">
         <f>IF(C35="","",$B$8&amp;" set app "&amp;A35&amp;"/"&amp;B35&amp;"  /"&amp;"applicationPool:"&amp;C35&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/uploader  /applicationPool:AXE_Test-Web</v>
@@ -1558,9 +1570,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
       <c r="H36" s="21" t="str">
         <f>IF(C36="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A36&amp;"/"&amp;B36&amp;"  /"&amp;"applicationPool:"&amp;C36&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/storage  /applicationPool:AXE_Test-Web</v>
@@ -1578,9 +1590,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="45"/>
       <c r="H37" s="21" t="str">
         <f t="shared" ref="H37:H38" si="4">IF(C37="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A37&amp;"/"&amp;B37&amp;"  /"&amp;"applicationPool:"&amp;C37&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/doc  /applicationPool:AXE_Test-Web</v>
@@ -1590,9 +1602,9 @@
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="17"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="38"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="45"/>
       <c r="H38" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -1654,7 +1666,7 @@
   <cols>
     <col min="1" max="1" width="34.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" style="11" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="11" bestFit="1" customWidth="1"/>
@@ -1666,11 +1678,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
       <c r="F1" s="12"/>
@@ -1689,7 +1701,7 @@
       <c r="D2" s="31"/>
       <c r="E2" s="31"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="40"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -1700,7 +1712,7 @@
       </c>
       <c r="C3" s="21"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="41"/>
+      <c r="G3" s="40"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -1711,7 +1723,7 @@
       </c>
       <c r="C4" s="21"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="41"/>
+      <c r="G4" s="40"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -1722,7 +1734,7 @@
       </c>
       <c r="C5" s="21"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="41"/>
+      <c r="G5" s="40"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
@@ -1733,14 +1745,14 @@
       </c>
       <c r="C6" s="21"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="41"/>
+      <c r="G6" s="40"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="12"/>
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
       <c r="D10" s="26"/>
       <c r="E10" s="26"/>
       <c r="F10" s="12"/>
@@ -1804,11 +1816,11 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
       <c r="F13" s="12"/>
@@ -1846,11 +1858,11 @@
       </c>
       <c r="D15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_ACC.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_ACC.mdf</v>
       </c>
       <c r="E15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_ACC.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_ACC.ldf</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="35" t="str">
@@ -1870,11 +1882,11 @@
 UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak' WHERE PhysicalPath IS NULL;
 set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak');
 set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak');
-RESTORE DATABASE AXE_CORE_2026_ACC FROM DISK = 'E:\BACKUP\AXE_CORE_2026_ACC.bak'
+RESTORE DATABASE AXE_CORE_2026_CT_ACC FROM DISK = 'E:\BACKUP\AXE_CORE_2026_ACC.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_ACC.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_ACC.ldf', REPLACE;EXEC AXE_CORE_2026_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_ACC.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_ACC.ldf', REPLACE;EXEC AXE_CORE_2026_CT_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CT_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1890,11 +1902,11 @@
       </c>
       <c r="D16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CLOUD.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_CLOUD.mdf</v>
       </c>
       <c r="E16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CLOUD.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_CLOUD.ldf</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="35" t="str">
@@ -1914,11 +1926,11 @@
 UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak' WHERE PhysicalPath IS NULL;
 set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak');
 set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak');
-RESTORE DATABASE AXE_CORE_2026_CLOUD FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak'
+RESTORE DATABASE AXE_CORE_2026_CT_CLOUD FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CLOUD.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CLOUD.ldf', REPLACE;EXEC AXE_CORE_2026_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CLOUD.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CLOUD.ldf', REPLACE;EXEC AXE_CORE_2026_CT_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CT_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1930,15 +1942,15 @@
         <v>E:\BACKUP\AXE_CORE_2026_CNF.bak</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D17" s="30" t="str">
         <f t="shared" ref="D17:D20" si="0">$B$4&amp;$C17&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CNF.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_CNF.mdf</v>
       </c>
       <c r="E17" s="30" t="str">
         <f t="shared" ref="E17:E20" si="1">$B$4&amp;$C17&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CNF.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_CNF.ldf</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="35" t="str">
@@ -1958,11 +1970,11 @@
 UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak' WHERE PhysicalPath IS NULL;
 set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak');
 set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak');
-RESTORE DATABASE AXE_CORE_2026_CNF.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CNF.bak'
+RESTORE DATABASE AXE_CORE_2026_CT_CNF FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CNF.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CNF.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CNF.bak.ldf', REPLACE;EXEC AXE_CORE_2026_CNF.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CNF.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CNF.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CNF.ldf', REPLACE;EXEC AXE_CORE_2026_CT_CNF.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CT_CNF.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1974,15 +1986,15 @@
         <v>E:\BACKUP\AXE_CORE_2026_LOG.bak</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D18" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_2026_LOG.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_LOG.mdf</v>
       </c>
       <c r="E18" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_2026_LOG.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_LOG.ldf</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="35" t="str">
@@ -1992,11 +2004,11 @@
 UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak' WHERE PhysicalPath IS NULL;
 set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak');
 set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak');
-RESTORE DATABASE AXE_CORE_2026_LOG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_LOG.bak'
+RESTORE DATABASE AXE_CORE_2026_CT_LOG FROM DISK = 'E:\BACKUP\AXE_CORE_2026_LOG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_LOG.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_LOG.bak.ldf', REPLACE;EXEC AXE_CORE_2026_LOG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_LOG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_LOG.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_LOG.ldf', REPLACE;EXEC AXE_CORE_2026_CT_LOG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CT_LOG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2008,15 +2020,15 @@
         <v>E:\BACKUP\AXE_CORE_2026_MSG.bak</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D19" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_2026_MSG.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_MSG.mdf</v>
       </c>
       <c r="E19" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_2026_MSG.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_MSG.ldf</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="35" t="str">
@@ -2026,11 +2038,11 @@
 UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak' WHERE PhysicalPath IS NULL;
 set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak');
 set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak');
-RESTORE DATABASE AXE_CORE_2026_MSG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_MSG.bak'
+RESTORE DATABASE AXE_CORE_2026_CT_MSG FROM DISK = 'E:\BACKUP\AXE_CORE_2026_MSG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_MSG.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_MSG.bak.ldf', REPLACE;EXEC AXE_CORE_2026_MSG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_MSG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_MSG.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_MSG.ldf', REPLACE;EXEC AXE_CORE_2026_CT_MSG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CT_MSG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2042,15 +2054,15 @@
         <v>E:\BACKUP\AXE_CORE_2026_STG.bak</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D20" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_2026_STG.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_STG.mdf</v>
       </c>
       <c r="E20" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_2026_STG.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CT_STG.ldf</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="35" t="str">
@@ -2060,11 +2072,11 @@
 UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak' WHERE PhysicalPath IS NULL;
 set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak');
 set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak');
-RESTORE DATABASE AXE_CORE_2026_STG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_STG.bak'
+RESTORE DATABASE AXE_CORE_2026_CT_STG FROM DISK = 'E:\BACKUP\AXE_CORE_2026_STG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_STG.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_STG.bak.ldf', REPLACE;EXEC AXE_CORE_2026_STG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_STG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_STG.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_STG.ldf', REPLACE;EXEC AXE_CORE_2026_CT_STG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CT_STG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
   </sheetData>

--- a/SQL/ExcelCauHinh/Settup AXE.xlsx
+++ b/SQL/ExcelCauHinh/Settup AXE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\ToolAXE\CauHinhHeThongAXE\SQL\ExcelCauHinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0B9549-308B-4421-BE2C-E92E26FF2934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C1D941-2115-46F0-83A5-FEA99A9ED844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cài đặt IIS" sheetId="2" r:id="rId1"/>
@@ -165,15 +165,9 @@
     <t>Đường dẫn gốc chứa file bak</t>
   </si>
   <si>
-    <t>E:\BACKUP\</t>
-  </si>
-  <si>
     <t>Đường dẫn gốc chứa database(mdf)</t>
   </si>
   <si>
-    <t>E:\DATABASE\</t>
-  </si>
-  <si>
     <t>Tên User mới</t>
   </si>
   <si>
@@ -321,40 +315,46 @@
     <t>http://localhost:1221</t>
   </si>
   <si>
-    <t>AXE_CORE_2026_ACC.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CLOUD.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CNF.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_LOG.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_MSG.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_STG.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CT_ACC</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CT_CLOUD</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CT_CNF</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CT_LOG</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CT_MSG</t>
-  </si>
-  <si>
-    <t>AXE_CORE_2026_CT_STG</t>
+    <t>AXE_2026_UBNDLANGCHANH_ACC.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_CLOUD.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_CNF.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_LOG.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_MSG.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_STG.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_ACC</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_CLOUD</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_CNF</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_LOG</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_MSG</t>
+  </si>
+  <si>
+    <t>AXE_2026_UBNDLANGCHANH_STG</t>
+  </si>
+  <si>
+    <t>D:\SohoaT10\Database\UBNDLANGCHANH\</t>
+  </si>
+  <si>
+    <t>D:\SohoaT10\Database\MDF\</t>
   </si>
 </sst>
 </file>
@@ -664,6 +664,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -681,12 +687,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1028,7 +1028,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C3" s="17"/>
       <c r="G3" s="12"/>
@@ -1039,7 +1039,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>6</v>
@@ -1052,7 +1052,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" s="17"/>
       <c r="G5" s="12"/>
@@ -1063,7 +1063,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>9</v>
@@ -1076,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>9</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C8" s="17"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="46"/>
+      <c r="H8" s="48"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
@@ -1152,7 +1152,7 @@
       <c r="C13" s="37"/>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
-      <c r="F13" s="50"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="12"/>
       <c r="H13" s="13"/>
     </row>
@@ -1261,10 +1261,10 @@
       <c r="D19" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="49"/>
+      <c r="F19" s="43"/>
       <c r="G19" s="12"/>
       <c r="H19" s="21" t="str">
         <f t="shared" ref="H19:H24" si="1">IF(D19="","",$B$8&amp;" add app  /site.name:"""&amp;B19&amp;""" /path:/"&amp;A19&amp;" /physicalPath:"&amp;C19&amp;"")</f>
@@ -1286,10 +1286,10 @@
       <c r="D20" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="49" t="s">
+      <c r="E20" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="49"/>
+      <c r="F20" s="43"/>
       <c r="G20" s="12"/>
       <c r="H20" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1311,10 +1311,10 @@
       <c r="D21" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="49" t="s">
+      <c r="E21" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="49"/>
+      <c r="F21" s="43"/>
       <c r="G21" s="12"/>
       <c r="H21" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1336,10 +1336,10 @@
       <c r="D22" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="49" t="s">
+      <c r="E22" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="49"/>
+      <c r="F22" s="43"/>
       <c r="G22" s="12"/>
       <c r="H22" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1361,10 +1361,10 @@
       <c r="D23" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="49" t="s">
+      <c r="E23" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="49"/>
+      <c r="F23" s="43"/>
       <c r="G23" s="12"/>
       <c r="H23" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1386,10 +1386,10 @@
       <c r="D24" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="49" t="s">
+      <c r="E24" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="49"/>
+      <c r="F24" s="43"/>
       <c r="G24" s="12"/>
       <c r="H24" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1401,8 +1401,8 @@
       <c r="B25" s="21"/>
       <c r="C25" s="17"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
       <c r="G25" s="12"/>
       <c r="H25" s="21"/>
     </row>
@@ -1471,11 +1471,11 @@
       <c r="C31" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
       <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1490,9 +1490,9 @@
         <f>$A$11</f>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
       <c r="H32" s="21" t="str">
         <f>IF(C32="","",$B$8&amp;" set app "&amp;A32&amp;"/"&amp;B32&amp;"  /"&amp;"applicationPool:"&amp;C32&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/login  /applicationPool:AXE_Test-Web</v>
@@ -1510,9 +1510,9 @@
         <f t="shared" ref="C33:C37" si="3">$A$11</f>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
       <c r="H33" s="21" t="str">
         <f>IF(C33="","",$B$8&amp;" set app "&amp;A33&amp;"/"&amp;B33&amp;"  /"&amp;"applicationPool:"&amp;C33&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/admin  /applicationPool:AXE_Test-Web</v>
@@ -1530,9 +1530,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
       <c r="H34" s="21" t="str">
         <f>IF(C34="","",$B$8&amp;" set app "&amp;A34&amp;"/"&amp;B34&amp;"  /"&amp;"applicationPool:"&amp;C34&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/resumable  /applicationPool:AXE_Test-Web</v>
@@ -1550,9 +1550,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
       <c r="H35" s="21" t="str">
         <f>IF(C35="","",$B$8&amp;" set app "&amp;A35&amp;"/"&amp;B35&amp;"  /"&amp;"applicationPool:"&amp;C35&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/uploader  /applicationPool:AXE_Test-Web</v>
@@ -1570,9 +1570,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
       <c r="H36" s="21" t="str">
         <f>IF(C36="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A36&amp;"/"&amp;B36&amp;"  /"&amp;"applicationPool:"&amp;C36&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/storage  /applicationPool:AXE_Test-Web</v>
@@ -1590,9 +1590,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="47"/>
       <c r="H37" s="21" t="str">
         <f t="shared" ref="H37:H38" si="4">IF(C37="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A37&amp;"/"&amp;B37&amp;"  /"&amp;"applicationPool:"&amp;C37&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/doc  /applicationPool:AXE_Test-Web</v>
@@ -1602,9 +1602,9 @@
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="17"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="47"/>
       <c r="H38" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -1612,13 +1612,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="H1:J1"/>
@@ -1635,6 +1628,13 @@
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K427:K1048576 G26:G426 K1:K25 B18 G9:G10" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1664,9 +1664,9 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5546875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="40.109375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="88" style="11" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" style="11" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="11" bestFit="1" customWidth="1"/>
@@ -1708,7 +1708,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C3" s="21"/>
       <c r="F3" s="12"/>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C4" s="21"/>
       <c r="F4" s="12"/>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="21"/>
       <c r="F5" s="12"/>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" s="32">
         <v>123456</v>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="31"/>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B9" s="21">
         <v>123456</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -1812,12 +1812,12 @@
       <c r="C12" s="34"/>
       <c r="F12" s="12"/>
       <c r="G12" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B13" s="37"/>
       <c r="C13" s="37"/>
@@ -1828,41 +1828,41 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="27" t="s">
         <v>57</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>59</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" s="27" t="str">
         <f>B3&amp;A15</f>
-        <v>E:\BACKUP\AXE_CORE_2026_ACC.bak</v>
+        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_ACC.mdf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.mdf</v>
       </c>
       <c r="E15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_ACC.ldf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.ldf</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="35" t="str">
@@ -1878,35 +1878,35 @@
 &amp;"EXEC "&amp;$C15&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C15&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_ACC.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak');
-RESTORE DATABASE AXE_CORE_2026_CT_ACC FROM DISK = 'E:\BACKUP\AXE_CORE_2026_ACC.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak''');
+UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak');
+RESTORE DATABASE AXE_2026_UBNDLANGCHANH_ACC FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_ACC.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_ACC.ldf', REPLACE;EXEC AXE_CORE_2026_CT_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CT_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.mdf',
+MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_UBNDLANGCHANH_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B16" s="30" t="str">
         <f>B3&amp;A16</f>
-        <v>E:\BACKUP\AXE_CORE_2026_CLOUD.bak</v>
+        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_CLOUD.mdf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.mdf</v>
       </c>
       <c r="E16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_CLOUD.ldf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.ldf</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="35" t="str">
@@ -1922,35 +1922,35 @@
 &amp;"EXEC "&amp;$C16&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C16&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_CLOUD.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak');
-RESTORE DATABASE AXE_CORE_2026_CT_CLOUD FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak''');
+UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak');
+RESTORE DATABASE AXE_2026_UBNDLANGCHANH_CLOUD FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CLOUD.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CLOUD.ldf', REPLACE;EXEC AXE_CORE_2026_CT_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CT_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.mdf',
+MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_UBNDLANGCHANH_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B17" s="30" t="str">
         <f>B3&amp;A17</f>
-        <v>E:\BACKUP\AXE_CORE_2026_CNF.bak</v>
+        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D17" s="30" t="str">
         <f t="shared" ref="D17:D20" si="0">$B$4&amp;$C17&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_CNF.mdf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.mdf</v>
       </c>
       <c r="E17" s="30" t="str">
         <f t="shared" ref="E17:E20" si="1">$B$4&amp;$C17&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_CNF.ldf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.ldf</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="35" t="str">
@@ -1966,117 +1966,117 @@
 &amp;"EXEC "&amp;$C17&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C17&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_CNF.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak');
-RESTORE DATABASE AXE_CORE_2026_CT_CNF FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CNF.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak''');
+UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak');
+RESTORE DATABASE AXE_2026_UBNDLANGCHANH_CNF FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CNF.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_CNF.ldf', REPLACE;EXEC AXE_CORE_2026_CT_CNF.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CT_CNF.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.mdf',
+MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_CNF.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_UBNDLANGCHANH_CNF.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B18" s="30" t="str">
         <f>B3&amp;A18</f>
-        <v>E:\BACKUP\AXE_CORE_2026_LOG.bak</v>
+        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D18" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_LOG.mdf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.mdf</v>
       </c>
       <c r="E18" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_LOG.ldf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.ldf</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_LOG.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak');
-RESTORE DATABASE AXE_CORE_2026_CT_LOG FROM DISK = 'E:\BACKUP\AXE_CORE_2026_LOG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak''');
+UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak');
+RESTORE DATABASE AXE_2026_UBNDLANGCHANH_LOG FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_LOG.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_LOG.ldf', REPLACE;EXEC AXE_CORE_2026_CT_LOG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CT_LOG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.mdf',
+MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_LOG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_UBNDLANGCHANH_LOG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B19" s="30" t="str">
         <f>B3&amp;A19</f>
-        <v>E:\BACKUP\AXE_CORE_2026_MSG.bak</v>
+        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_MSG.mdf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.mdf</v>
       </c>
       <c r="E19" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_MSG.ldf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.ldf</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_MSG.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak');
-RESTORE DATABASE AXE_CORE_2026_CT_MSG FROM DISK = 'E:\BACKUP\AXE_CORE_2026_MSG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak''');
+UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak');
+RESTORE DATABASE AXE_2026_UBNDLANGCHANH_MSG FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_MSG.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_MSG.ldf', REPLACE;EXEC AXE_CORE_2026_CT_MSG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CT_MSG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.mdf',
+MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_MSG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_UBNDLANGCHANH_MSG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B20" s="30" t="str">
         <f>B3&amp;A20</f>
-        <v>E:\BACKUP\AXE_CORE_2026_STG.bak</v>
+        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D20" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_STG.mdf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.mdf</v>
       </c>
       <c r="E20" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_2026_CT_STG.ldf</v>
+        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.ldf</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_STG.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak');
-RESTORE DATABASE AXE_CORE_2026_CT_STG FROM DISK = 'E:\BACKUP\AXE_CORE_2026_STG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak''');
+UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak');
+RESTORE DATABASE AXE_2026_UBNDLANGCHANH_STG FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_STG.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CT_STG.ldf', REPLACE;EXEC AXE_CORE_2026_CT_STG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_2026_CT_STG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.mdf',
+MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_STG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_UBNDLANGCHANH_STG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
   </sheetData>
@@ -2129,43 +2129,43 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" s="9"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" s="9"/>
     </row>
@@ -2209,7 +2209,7 @@
       <c r="C2" s="54"/>
       <c r="G2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>17</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="2" t="str">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="2" t="str">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="2" t="str">
@@ -2500,10 +2500,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="2" t="str">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="2" t="str">
@@ -2546,10 +2546,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="2" t="str">
@@ -2569,10 +2569,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="2" t="str">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="2" t="str">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="2" t="str">
@@ -2638,10 +2638,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="2" t="str">
@@ -2671,7 +2671,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="54" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -2689,11 +2689,11 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H30" s="2" t="str">
         <f>IF(C30="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A30&amp;"/  /"&amp;"applicationPool:"&amp;C30&amp;"")</f>
@@ -2702,11 +2702,11 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H31" s="2" t="str">
         <f t="shared" ref="H31:H39" si="2">IF(C31="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A31&amp;"/  /"&amp;"applicationPool:"&amp;C31&amp;"")</f>
@@ -2715,11 +2715,11 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H32" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2728,11 +2728,11 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H33" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2741,11 +2741,11 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H34" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2754,11 +2754,11 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H35" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2767,11 +2767,11 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H36" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2780,11 +2780,11 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H37" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2793,11 +2793,11 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H38" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2806,11 +2806,11 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H39" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2843,27 +2843,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Ghich_x00fa_ xmlns="97d068c0-5bfb-413b-9996-819e39fdf128" xsi:nil="true"/>
-    <TaxCatchAll xmlns="2c7f0914-2907-4374-a90b-da4fc7d9e6d0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="97d068c0-5bfb-413b-9996-819e39fdf128">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010097FE9C0C8E574444875F1CBBF8414DDA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c7e0992f45b677c2156c5ab52d17057f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="97d068c0-5bfb-413b-9996-819e39fdf128" xmlns:ns3="2c7f0914-2907-4374-a90b-da4fc7d9e6d0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f06a3ea3329379ac3c4a4f5da7fed49" ns2:_="" ns3:_="">
     <xsd:import namespace="97d068c0-5bfb-413b-9996-819e39fdf128"/>
@@ -3098,10 +3077,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Ghich_x00fa_ xmlns="97d068c0-5bfb-413b-9996-819e39fdf128" xsi:nil="true"/>
+    <TaxCatchAll xmlns="2c7f0914-2907-4374-a90b-da4fc7d9e6d0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="97d068c0-5bfb-413b-9996-819e39fdf128">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FDEE16B-9D1D-4FD0-B127-E14D995BDF2D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E3A15DF-6B1B-40AC-992D-CB264AF46DCF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="97d068c0-5bfb-413b-9996-819e39fdf128"/>
+    <ds:schemaRef ds:uri="2c7f0914-2907-4374-a90b-da4fc7d9e6d0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3118,20 +3129,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E3A15DF-6B1B-40AC-992D-CB264AF46DCF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FDEE16B-9D1D-4FD0-B127-E14D995BDF2D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="97d068c0-5bfb-413b-9996-819e39fdf128"/>
-    <ds:schemaRef ds:uri="2c7f0914-2907-4374-a90b-da4fc7d9e6d0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/SQL/ExcelCauHinh/Settup AXE.xlsx
+++ b/SQL/ExcelCauHinh/Settup AXE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\ToolAXE\CauHinhHeThongAXE\SQL\ExcelCauHinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C1D941-2115-46F0-83A5-FEA99A9ED844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C883A351-5238-404B-8F78-EB2AA6382441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,46 +315,46 @@
     <t>http://localhost:1221</t>
   </si>
   <si>
-    <t>AXE_2026_UBNDLANGCHANH_ACC.bak</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_CLOUD.bak</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_CNF.bak</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_LOG.bak</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_MSG.bak</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_STG.bak</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_ACC</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_CLOUD</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_CNF</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_LOG</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_MSG</t>
-  </si>
-  <si>
-    <t>AXE_2026_UBNDLANGCHANH_STG</t>
-  </si>
-  <si>
-    <t>D:\SohoaT10\Database\UBNDLANGCHANH\</t>
-  </si>
-  <si>
-    <t>D:\SohoaT10\Database\MDF\</t>
+    <t>C:\SoHoaThaiNguyen\Database\BackupSQL\</t>
+  </si>
+  <si>
+    <t>C:\SoHoaThaiNguyen\Database\MDF</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_ACC.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_CLOUD.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_CNF.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_LOG.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_MSG.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_STG.bak</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_ACC</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_CLOUD</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_CNF</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_LOG</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_MSG</t>
+  </si>
+  <si>
+    <t>AXE_2026_THAINGUYEN_STG</t>
   </si>
 </sst>
 </file>
@@ -1708,7 +1708,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C3" s="21"/>
       <c r="F3" s="12"/>
@@ -1719,7 +1719,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C4" s="21"/>
       <c r="F4" s="12"/>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B15" s="27" t="str">
         <f>B3&amp;A15</f>
-        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak</v>
+        <v>C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_ACC.bak</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".mdf"</f>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.mdf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_ACC.mdf</v>
       </c>
       <c r="E15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".ldf"</f>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.ldf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_ACC.ldf</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="35" t="str">
@@ -1878,35 +1878,35 @@
 &amp;"EXEC "&amp;$C15&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C15&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak''');
-UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak');
-RESTORE DATABASE AXE_2026_UBNDLANGCHANH_ACC FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_ACC.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_ACC.bak''');
+UPDATE #FileList SET PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_ACC.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_ACC.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_ACC.bak');
+RESTORE DATABASE AXE_2026_THAINGUYEN_ACC FROM DISK = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_ACC.bak'
 WITH 
-MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.mdf',
-MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_ACC.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_2026_UBNDLANGCHANH_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_ACC.mdf',
+MOVE @LogLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_ACC.ldf', REPLACE;EXEC AXE_2026_THAINGUYEN_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_THAINGUYEN_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B16" s="30" t="str">
         <f>B3&amp;A16</f>
-        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak</v>
+        <v>C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CLOUD.bak</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".mdf"</f>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.mdf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CLOUD.mdf</v>
       </c>
       <c r="E16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".ldf"</f>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.ldf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CLOUD.ldf</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="35" t="str">
@@ -1922,35 +1922,35 @@
 &amp;"EXEC "&amp;$C16&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C16&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak''');
-UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak');
-RESTORE DATABASE AXE_2026_UBNDLANGCHANH_CLOUD FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CLOUD.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CLOUD.bak''');
+UPDATE #FileList SET PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CLOUD.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CLOUD.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CLOUD.bak');
+RESTORE DATABASE AXE_2026_THAINGUYEN_CLOUD FROM DISK = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CLOUD.bak'
 WITH 
-MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.mdf',
-MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CLOUD.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_2026_UBNDLANGCHANH_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CLOUD.mdf',
+MOVE @LogLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CLOUD.ldf', REPLACE;EXEC AXE_2026_THAINGUYEN_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_THAINGUYEN_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" s="30" t="str">
         <f>B3&amp;A17</f>
-        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak</v>
+        <v>C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CNF.bak</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D17" s="30" t="str">
         <f t="shared" ref="D17:D20" si="0">$B$4&amp;$C17&amp;".mdf"</f>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.mdf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CNF.mdf</v>
       </c>
       <c r="E17" s="30" t="str">
         <f t="shared" ref="E17:E20" si="1">$B$4&amp;$C17&amp;".ldf"</f>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.ldf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CNF.ldf</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="35" t="str">
@@ -1966,117 +1966,117 @@
 &amp;"EXEC "&amp;$C17&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C17&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak''');
-UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak');
-RESTORE DATABASE AXE_2026_UBNDLANGCHANH_CNF FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_CNF.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CNF.bak''');
+UPDATE #FileList SET PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CNF.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CNF.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CNF.bak');
+RESTORE DATABASE AXE_2026_THAINGUYEN_CNF FROM DISK = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_CNF.bak'
 WITH 
-MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.mdf',
-MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_CNF.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_CNF.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_2026_UBNDLANGCHANH_CNF.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CNF.mdf',
+MOVE @LogLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_CNF.ldf', REPLACE;EXEC AXE_2026_THAINGUYEN_CNF.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_THAINGUYEN_CNF.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B18" s="30" t="str">
         <f>B3&amp;A18</f>
-        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak</v>
+        <v>C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_LOG.bak</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D18" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.mdf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_LOG.mdf</v>
       </c>
       <c r="E18" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.ldf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_LOG.ldf</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak''');
-UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak');
-RESTORE DATABASE AXE_2026_UBNDLANGCHANH_LOG FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_LOG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_LOG.bak''');
+UPDATE #FileList SET PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_LOG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_LOG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_LOG.bak');
+RESTORE DATABASE AXE_2026_THAINGUYEN_LOG FROM DISK = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_LOG.bak'
 WITH 
-MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.mdf',
-MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_LOG.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_LOG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_2026_UBNDLANGCHANH_LOG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_LOG.mdf',
+MOVE @LogLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_LOG.ldf', REPLACE;EXEC AXE_2026_THAINGUYEN_LOG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_THAINGUYEN_LOG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B19" s="30" t="str">
         <f>B3&amp;A19</f>
-        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak</v>
+        <v>C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_MSG.bak</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.mdf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_MSG.mdf</v>
       </c>
       <c r="E19" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.ldf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_MSG.ldf</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak''');
-UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak');
-RESTORE DATABASE AXE_2026_UBNDLANGCHANH_MSG FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_MSG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_MSG.bak''');
+UPDATE #FileList SET PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_MSG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_MSG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_MSG.bak');
+RESTORE DATABASE AXE_2026_THAINGUYEN_MSG FROM DISK = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_MSG.bak'
 WITH 
-MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.mdf',
-MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_MSG.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_MSG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_2026_UBNDLANGCHANH_MSG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_MSG.mdf',
+MOVE @LogLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_MSG.ldf', REPLACE;EXEC AXE_2026_THAINGUYEN_MSG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_THAINGUYEN_MSG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B20" s="30" t="str">
         <f>B3&amp;A20</f>
-        <v>D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak</v>
+        <v>C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_STG.bak</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.mdf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_STG.mdf</v>
       </c>
       <c r="E20" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.ldf</v>
+        <v>C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_STG.ldf</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak''');
-UPDATE #FileList SET PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak');
-RESTORE DATABASE AXE_2026_UBNDLANGCHANH_STG FROM DISK = 'D:\SohoaT10\Database\UBNDLANGCHANH\AXE_2026_UBNDLANGCHANH_STG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_STG.bak''');
+UPDATE #FileList SET PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_STG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_STG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_STG.bak');
+RESTORE DATABASE AXE_2026_THAINGUYEN_STG FROM DISK = 'C:\SoHoaThaiNguyen\Database\BackupSQL\AXE_2026_THAINGUYEN_STG.bak'
 WITH 
-MOVE @DataLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.mdf',
-MOVE @LogLogicalName TO 'D:\SohoaT10\Database\MDF\AXE_2026_UBNDLANGCHANH_STG.ldf', REPLACE;EXEC AXE_2026_UBNDLANGCHANH_STG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_2026_UBNDLANGCHANH_STG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_STG.mdf',
+MOVE @LogLogicalName TO 'C:\SoHoaThaiNguyen\Database\MDFAXE_2026_THAINGUYEN_STG.ldf', REPLACE;EXEC AXE_2026_THAINGUYEN_STG.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_2026_THAINGUYEN_STG.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
   </sheetData>
